--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11883" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11921" uniqueCount="824">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T12:03:31+00:00</t>
+    <t>2026-02-04T14:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -717,14 +717,14 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
-    <t>Person, die die Richtigkeit der Zusammenstellung bestätigt.</t>
-  </si>
-  <si>
-    <t>Person, die die Richtigkeit der Zusammenstellung bestätigt. Darf bei automatischer Erstellung durch ein Device nicht angegeben werden.</t>
+    <t>Autor der Austrian Patient Summary</t>
+  </si>
+  <si>
+    <t>Autor der Austrian Patient Summary. Ggf. Angabe eines Devices z.B. bei automatischer Erstellung der Patient Summary durch die zentrale Anwendung.</t>
   </si>
   <si>
     <t>Identifies who is responsible for the content.</t>
@@ -801,10 +801,10 @@
 </t>
   </si>
   <si>
-    <t>Attests to accuracy of composition</t>
-  </si>
-  <si>
-    <t>A participant who has attested to the accuracy of the composition/document.</t>
+    <t>Person, die die Richtigkeit der Zusammenstellung bestätigt.</t>
+  </si>
+  <si>
+    <t>Person, die die Richtigkeit der Zusammenstellung bestätigt. Darf bei automatischer Erstellung durch ein Device nicht angegeben werden.</t>
   </si>
   <si>
     <t>Only list each attester once.</t>
@@ -905,7 +905,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1016,7 +1016,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
+Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -1136,7 +1136,7 @@
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
@@ -1412,9 +1412,6 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>Composition.section:sectionMedications.entry:medicationStatement</t>
   </si>
   <si>
@@ -2234,7 +2231,7 @@
     <t>Composition.section:sectionPlanOfCare.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunizationrecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -2245,6 +2242,16 @@
   </si>
   <si>
     <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan)
+</t>
+  </si>
+  <si>
+    <t>Composition.section:sectionPlanOfCare.entry:immunizationRecommendation</t>
+  </si>
+  <si>
+    <t>immunizationRecommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunizationrecommendation)
 </t>
   </si>
   <si>
@@ -2943,7 +2950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO317"/>
+  <dimension ref="A1:AO318"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.23828125" customWidth="true" bestFit="true"/>
@@ -7880,7 +7887,7 @@
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
         <v>363</v>
@@ -10821,10 +10828,10 @@
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>413</v>
@@ -10859,13 +10866,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -10887,7 +10894,7 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>414</v>
@@ -10978,13 +10985,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -11006,7 +11013,7 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>414</v>
@@ -11097,13 +11104,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
@@ -11125,7 +11132,7 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>414</v>
@@ -11216,13 +11223,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
@@ -11244,7 +11251,7 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>414</v>
@@ -11335,13 +11342,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>79</v>
@@ -11363,7 +11370,7 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>414</v>
@@ -11454,7 +11461,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>420</v>
@@ -11573,7 +11580,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>428</v>
@@ -11690,13 +11697,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
@@ -11721,10 +11728,10 @@
         <v>253</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11807,7 +11814,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>367</v>
@@ -11922,7 +11929,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>368</v>
@@ -12039,7 +12046,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>369</v>
@@ -12158,7 +12165,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>370</v>
@@ -12277,7 +12284,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>376</v>
@@ -12325,7 +12332,7 @@
         <v>79</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>79</v>
@@ -12396,7 +12403,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>383</v>
@@ -12513,7 +12520,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>386</v>
@@ -12630,7 +12637,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>391</v>
@@ -12747,7 +12754,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>397</v>
@@ -12866,7 +12873,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>405</v>
@@ -12985,7 +12992,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>413</v>
@@ -13011,7 +13018,7 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>414</v>
@@ -13062,10 +13069,10 @@
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>413</v>
@@ -13100,13 +13107,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
@@ -13128,7 +13135,7 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>414</v>
@@ -13219,13 +13226,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13247,7 +13254,7 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>414</v>
@@ -13338,7 +13345,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>420</v>
@@ -13457,7 +13464,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>428</v>
@@ -13574,13 +13581,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>79</v>
@@ -13605,10 +13612,10 @@
         <v>253</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13691,7 +13698,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>367</v>
@@ -13806,7 +13813,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>368</v>
@@ -13923,7 +13930,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>369</v>
@@ -14042,7 +14049,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>370</v>
@@ -14161,7 +14168,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>376</v>
@@ -14209,7 +14216,7 @@
         <v>79</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>79</v>
@@ -14280,7 +14287,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>383</v>
@@ -14397,7 +14404,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>386</v>
@@ -14514,7 +14521,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>391</v>
@@ -14631,7 +14638,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>397</v>
@@ -14750,7 +14757,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>405</v>
@@ -14869,7 +14876,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>413</v>
@@ -14895,7 +14902,7 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>414</v>
@@ -14946,10 +14953,10 @@
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>413</v>
@@ -14984,13 +14991,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -15012,7 +15019,7 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>414</v>
@@ -15103,13 +15110,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -15131,7 +15138,7 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>414</v>
@@ -15222,7 +15229,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>420</v>
@@ -15341,7 +15348,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>428</v>
@@ -15458,13 +15465,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>79</v>
@@ -15489,10 +15496,10 @@
         <v>253</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15555,7 +15562,7 @@
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -15575,7 +15582,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>367</v>
@@ -15690,7 +15697,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>368</v>
@@ -15807,7 +15814,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>369</v>
@@ -15926,7 +15933,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>370</v>
@@ -16045,7 +16052,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>376</v>
@@ -16093,7 +16100,7 @@
         <v>79</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>79</v>
@@ -16164,7 +16171,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>383</v>
@@ -16281,7 +16288,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>386</v>
@@ -16398,7 +16405,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>391</v>
@@ -16515,7 +16522,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>397</v>
@@ -16634,7 +16641,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>405</v>
@@ -16753,7 +16760,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>413</v>
@@ -16779,7 +16786,7 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>414</v>
@@ -16830,10 +16837,10 @@
       </c>
       <c r="AC118" s="2"/>
       <c r="AD118" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF118" t="s" s="2">
         <v>413</v>
@@ -16868,13 +16875,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>79</v>
@@ -16896,7 +16903,7 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>414</v>
@@ -16987,13 +16994,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>79</v>
@@ -17015,7 +17022,7 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>414</v>
@@ -17106,7 +17113,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>420</v>
@@ -17225,7 +17232,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>428</v>
@@ -17342,13 +17349,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>79</v>
@@ -17373,10 +17380,10 @@
         <v>253</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17439,7 +17446,7 @@
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
@@ -17459,7 +17466,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>367</v>
@@ -17574,7 +17581,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>368</v>
@@ -17691,7 +17698,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>369</v>
@@ -17810,7 +17817,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>370</v>
@@ -17929,7 +17936,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>376</v>
@@ -17977,7 +17984,7 @@
         <v>79</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>79</v>
@@ -18048,7 +18055,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>383</v>
@@ -18165,7 +18172,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>386</v>
@@ -18282,7 +18289,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>391</v>
@@ -18399,7 +18406,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>397</v>
@@ -18518,7 +18525,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>405</v>
@@ -18637,7 +18644,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>413</v>
@@ -18663,7 +18670,7 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>414</v>
@@ -18714,10 +18721,10 @@
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF134" t="s" s="2">
         <v>413</v>
@@ -18752,13 +18759,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>79</v>
@@ -18780,7 +18787,7 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>414</v>
@@ -18871,13 +18878,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>79</v>
@@ -18899,7 +18906,7 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>414</v>
@@ -18990,7 +18997,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>420</v>
@@ -19109,7 +19116,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>428</v>
@@ -19226,13 +19233,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>79</v>
@@ -19257,10 +19264,10 @@
         <v>253</v>
       </c>
       <c r="L139" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19343,7 +19350,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>367</v>
@@ -19458,7 +19465,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>368</v>
@@ -19575,7 +19582,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>369</v>
@@ -19694,7 +19701,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>370</v>
@@ -19813,7 +19820,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>376</v>
@@ -19861,7 +19868,7 @@
         <v>79</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>79</v>
@@ -19932,7 +19939,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>383</v>
@@ -20049,7 +20056,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>386</v>
@@ -20166,7 +20173,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>391</v>
@@ -20283,7 +20290,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>397</v>
@@ -20402,7 +20409,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>405</v>
@@ -20521,7 +20528,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>413</v>
@@ -20547,7 +20554,7 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>414</v>
@@ -20598,10 +20605,10 @@
       </c>
       <c r="AC150" s="2"/>
       <c r="AD150" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF150" t="s" s="2">
         <v>413</v>
@@ -20636,13 +20643,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>79</v>
@@ -20664,7 +20671,7 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>414</v>
@@ -20755,13 +20762,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -20783,7 +20790,7 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>414</v>
@@ -20874,7 +20881,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>420</v>
@@ -20993,7 +21000,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>428</v>
@@ -21110,13 +21117,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
@@ -21141,10 +21148,10 @@
         <v>253</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21227,7 +21234,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>367</v>
@@ -21342,7 +21349,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>368</v>
@@ -21459,7 +21466,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>369</v>
@@ -21578,7 +21585,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>370</v>
@@ -21697,7 +21704,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>376</v>
@@ -21745,7 +21752,7 @@
         <v>79</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>79</v>
@@ -21816,7 +21823,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>383</v>
@@ -21933,7 +21940,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>386</v>
@@ -22050,7 +22057,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>391</v>
@@ -22167,7 +22174,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>397</v>
@@ -22286,7 +22293,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>405</v>
@@ -22405,7 +22412,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>413</v>
@@ -22431,7 +22438,7 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>414</v>
@@ -22478,11 +22485,11 @@
         <v>79</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AC166" s="2"/>
       <c r="AD166" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE166" t="s" s="2">
         <v>363</v>
@@ -22520,13 +22527,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>79</v>
@@ -22548,7 +22555,7 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L167" t="s" s="2">
         <v>414</v>
@@ -22639,13 +22646,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>79</v>
@@ -22667,7 +22674,7 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L168" t="s" s="2">
         <v>414</v>
@@ -22758,13 +22765,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>79</v>
@@ -22786,7 +22793,7 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>414</v>
@@ -22877,13 +22884,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>79</v>
@@ -22905,7 +22912,7 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L170" t="s" s="2">
         <v>414</v>
@@ -22996,7 +23003,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>420</v>
@@ -23115,7 +23122,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>428</v>
@@ -23232,13 +23239,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>79</v>
@@ -23263,10 +23270,10 @@
         <v>253</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23349,7 +23356,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>367</v>
@@ -23464,7 +23471,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>368</v>
@@ -23581,7 +23588,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>369</v>
@@ -23700,7 +23707,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>370</v>
@@ -23819,7 +23826,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>376</v>
@@ -23867,7 +23874,7 @@
         <v>79</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>79</v>
@@ -23938,7 +23945,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>383</v>
@@ -24055,7 +24062,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>386</v>
@@ -24172,7 +24179,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>391</v>
@@ -24289,7 +24296,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>397</v>
@@ -24408,7 +24415,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>405</v>
@@ -24527,7 +24534,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>413</v>
@@ -24553,7 +24560,7 @@
         <v>79</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="L184" t="s" s="2">
         <v>414</v>
@@ -24604,7 +24611,7 @@
       </c>
       <c r="AC184" s="2"/>
       <c r="AD184" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE184" t="s" s="2">
         <v>363</v>
@@ -24642,13 +24649,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>79</v>
@@ -24670,7 +24677,7 @@
         <v>79</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>414</v>
@@ -24761,13 +24768,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>79</v>
@@ -24789,7 +24796,7 @@
         <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>414</v>
@@ -24880,7 +24887,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>420</v>
@@ -24999,7 +25006,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>428</v>
@@ -25116,13 +25123,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>79</v>
@@ -25147,10 +25154,10 @@
         <v>253</v>
       </c>
       <c r="L189" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M189" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M189" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -25233,7 +25240,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>367</v>
@@ -25348,7 +25355,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>368</v>
@@ -25465,7 +25472,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>369</v>
@@ -25584,7 +25591,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>370</v>
@@ -25703,7 +25710,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>376</v>
@@ -25751,7 +25758,7 @@
         <v>79</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>79</v>
@@ -25822,7 +25829,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>383</v>
@@ -25939,7 +25946,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>386</v>
@@ -26056,7 +26063,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>391</v>
@@ -26173,7 +26180,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>397</v>
@@ -26292,7 +26299,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>405</v>
@@ -26411,7 +26418,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>413</v>
@@ -26437,7 +26444,7 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L200" t="s" s="2">
         <v>414</v>
@@ -26488,10 +26495,10 @@
       </c>
       <c r="AC200" s="2"/>
       <c r="AD200" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF200" t="s" s="2">
         <v>413</v>
@@ -26526,13 +26533,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>79</v>
@@ -26554,7 +26561,7 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L201" t="s" s="2">
         <v>414</v>
@@ -26645,13 +26652,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>79</v>
@@ -26673,7 +26680,7 @@
         <v>79</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L202" t="s" s="2">
         <v>414</v>
@@ -26764,7 +26771,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>420</v>
@@ -26883,7 +26890,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>428</v>
@@ -27000,13 +27007,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
@@ -27031,10 +27038,10 @@
         <v>253</v>
       </c>
       <c r="L205" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M205" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="M205" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
@@ -27117,7 +27124,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>367</v>
@@ -27232,7 +27239,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>368</v>
@@ -27349,7 +27356,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>369</v>
@@ -27468,7 +27475,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>370</v>
@@ -27587,7 +27594,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>376</v>
@@ -27635,7 +27642,7 @@
         <v>79</v>
       </c>
       <c r="S210" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="T210" t="s" s="2">
         <v>79</v>
@@ -27706,7 +27713,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>383</v>
@@ -27823,7 +27830,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>386</v>
@@ -27940,7 +27947,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>391</v>
@@ -28057,7 +28064,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>397</v>
@@ -28176,7 +28183,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>405</v>
@@ -28295,7 +28302,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>413</v>
@@ -28321,7 +28328,7 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="L216" t="s" s="2">
         <v>414</v>
@@ -28372,10 +28379,10 @@
       </c>
       <c r="AC216" s="2"/>
       <c r="AD216" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF216" t="s" s="2">
         <v>413</v>
@@ -28410,13 +28417,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>79</v>
@@ -28438,7 +28445,7 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L217" t="s" s="2">
         <v>414</v>
@@ -28529,13 +28536,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>79</v>
@@ -28557,7 +28564,7 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>414</v>
@@ -28648,13 +28655,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>79</v>
@@ -28676,7 +28683,7 @@
         <v>79</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="L219" t="s" s="2">
         <v>414</v>
@@ -28767,7 +28774,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>420</v>
@@ -28886,7 +28893,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>428</v>
@@ -29003,13 +29010,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -29034,10 +29041,10 @@
         <v>253</v>
       </c>
       <c r="L222" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M222" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="M222" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -29120,7 +29127,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>367</v>
@@ -29235,7 +29242,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>368</v>
@@ -29352,7 +29359,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>369</v>
@@ -29471,7 +29478,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>370</v>
@@ -29590,7 +29597,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>376</v>
@@ -29638,7 +29645,7 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="T227" t="s" s="2">
         <v>79</v>
@@ -29709,7 +29716,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>383</v>
@@ -29826,7 +29833,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>386</v>
@@ -29943,7 +29950,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>391</v>
@@ -30060,7 +30067,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>397</v>
@@ -30179,7 +30186,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>405</v>
@@ -30298,7 +30305,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>413</v>
@@ -30324,7 +30331,7 @@
         <v>79</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L233" t="s" s="2">
         <v>414</v>
@@ -30375,10 +30382,10 @@
       </c>
       <c r="AC233" s="2"/>
       <c r="AD233" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="AF233" t="s" s="2">
         <v>413</v>
@@ -30413,13 +30420,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D234" t="s" s="2">
         <v>79</v>
@@ -30441,7 +30448,7 @@
         <v>79</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L234" t="s" s="2">
         <v>414</v>
@@ -30532,13 +30539,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>465</v>
+        <v>704</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>79</v>
@@ -30560,7 +30567,7 @@
         <v>79</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>466</v>
+        <v>705</v>
       </c>
       <c r="L235" t="s" s="2">
         <v>414</v>
@@ -30651,12 +30658,14 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C236" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D236" t="s" s="2">
         <v>79</v>
       </c>
@@ -30665,7 +30674,7 @@
         <v>80</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>79</v>
@@ -30677,20 +30686,18 @@
         <v>79</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>79</v>
       </c>
@@ -30714,13 +30721,13 @@
         <v>79</v>
       </c>
       <c r="X236" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>79</v>
@@ -30738,13 +30745,13 @@
         <v>79</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>417</v>
@@ -30756,10 +30763,10 @@
         <v>79</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM236" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN236" t="s" s="2">
         <v>79</v>
@@ -30770,10 +30777,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30784,7 +30791,7 @@
         <v>80</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>79</v>
@@ -30796,18 +30803,20 @@
         <v>79</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O237" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P237" t="s" s="2">
         <v>79</v>
       </c>
@@ -30831,13 +30840,13 @@
         <v>79</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>79</v>
@@ -30855,16 +30864,16 @@
         <v>79</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>103</v>
@@ -30873,10 +30882,10 @@
         <v>79</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN237" t="s" s="2">
         <v>79</v>
@@ -30887,14 +30896,12 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
         <v>79</v>
       </c>
@@ -30903,7 +30910,7 @@
         <v>80</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>79</v>
@@ -30915,15 +30922,17 @@
         <v>79</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>709</v>
+        <v>429</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N238" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>79</v>
@@ -30972,7 +30981,7 @@
         <v>79</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
@@ -30981,10 +30990,10 @@
         <v>81</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>79</v>
@@ -30993,7 +31002,7 @@
         <v>365</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>79</v>
@@ -31004,12 +31013,14 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C239" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C239" t="s" s="2">
+        <v>710</v>
+      </c>
       <c r="D239" t="s" s="2">
         <v>79</v>
       </c>
@@ -31030,13 +31041,13 @@
         <v>79</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>262</v>
+        <v>711</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>263</v>
+        <v>712</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -31087,28 +31098,28 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI239" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>79</v>
@@ -31119,21 +31130,21 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>79</v>
@@ -31145,17 +31156,15 @@
         <v>79</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -31204,19 +31213,19 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>79</v>
@@ -31236,14 +31245,14 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -31256,26 +31265,24 @@
         <v>79</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K241" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N241" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O241" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>79</v>
       </c>
@@ -31323,7 +31330,7 @@
         <v>79</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>80</v>
@@ -31341,7 +31348,7 @@
         <v>79</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM241" t="s" s="2">
         <v>79</v>
@@ -31355,45 +31362,45 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I242" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>79</v>
@@ -31442,28 +31449,28 @@
         <v>79</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>79</v>
@@ -31474,18 +31481,18 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G243" t="s" s="2">
         <v>91</v>
@@ -31500,19 +31507,19 @@
         <v>79</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>79</v>
@@ -31522,7 +31529,7 @@
         <v>79</v>
       </c>
       <c r="S243" t="s" s="2">
-        <v>716</v>
+        <v>79</v>
       </c>
       <c r="T243" t="s" s="2">
         <v>79</v>
@@ -31537,13 +31544,13 @@
         <v>79</v>
       </c>
       <c r="X243" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>79</v>
@@ -31561,7 +31568,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -31579,10 +31586,10 @@
         <v>79</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>79</v>
@@ -31596,7 +31603,7 @@
         <v>717</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31604,10 +31611,10 @@
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>79</v>
@@ -31619,17 +31626,19 @@
         <v>79</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N244" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N244" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O244" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>79</v>
@@ -31639,7 +31648,7 @@
         <v>79</v>
       </c>
       <c r="S244" t="s" s="2">
-        <v>79</v>
+        <v>718</v>
       </c>
       <c r="T244" t="s" s="2">
         <v>79</v>
@@ -31654,13 +31663,13 @@
         <v>79</v>
       </c>
       <c r="X244" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>79</v>
@@ -31678,13 +31687,13 @@
         <v>79</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>79</v>
@@ -31696,24 +31705,24 @@
         <v>79</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO244" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31724,7 +31733,7 @@
         <v>80</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>79</v>
@@ -31736,18 +31745,18 @@
         <v>79</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O245" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P245" t="s" s="2">
         <v>79</v>
       </c>
@@ -31795,13 +31804,13 @@
         <v>79</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>79</v>
@@ -31813,24 +31822,24 @@
         <v>79</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31853,16 +31862,16 @@
         <v>79</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -31912,7 +31921,7 @@
         <v>79</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -31921,7 +31930,7 @@
         <v>91</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>103</v>
@@ -31930,10 +31939,10 @@
         <v>79</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM246" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN246" t="s" s="2">
         <v>79</v>
@@ -31944,10 +31953,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -31970,20 +31979,18 @@
         <v>79</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>79</v>
       </c>
@@ -32007,13 +32014,13 @@
         <v>79</v>
       </c>
       <c r="X247" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>79</v>
@@ -32031,7 +32038,7 @@
         <v>79</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -32040,7 +32047,7 @@
         <v>91</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>103</v>
@@ -32049,24 +32056,24 @@
         <v>79</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32089,19 +32096,19 @@
         <v>79</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O248" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>79</v>
@@ -32126,13 +32133,13 @@
         <v>79</v>
       </c>
       <c r="X248" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y248" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>79</v>
@@ -32150,7 +32157,7 @@
         <v>79</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -32168,7 +32175,7 @@
         <v>79</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM248" t="s" s="2">
         <v>168</v>
@@ -32177,15 +32184,15 @@
         <v>79</v>
       </c>
       <c r="AO248" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32196,7 +32203,7 @@
         <v>80</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>79</v>
@@ -32208,18 +32215,20 @@
         <v>79</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>631</v>
+        <v>172</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N249" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O249" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P249" t="s" s="2">
         <v>79</v>
       </c>
@@ -32243,38 +32252,40 @@
         <v>79</v>
       </c>
       <c r="X249" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y249" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z249" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA249" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC249" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD249" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH249" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>103</v>
@@ -32283,10 +32294,10 @@
         <v>79</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM249" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN249" t="s" s="2">
         <v>79</v>
@@ -32297,14 +32308,12 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C250" t="s" s="2">
-        <v>724</v>
-      </c>
+      <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
         <v>79</v>
       </c>
@@ -32313,7 +32322,7 @@
         <v>80</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H250" t="s" s="2">
         <v>79</v>
@@ -32325,7 +32334,7 @@
         <v>79</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>725</v>
+        <v>630</v>
       </c>
       <c r="L250" t="s" s="2">
         <v>414</v>
@@ -32372,16 +32381,14 @@
         <v>79</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC250" s="2"/>
       <c r="AD250" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE250" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF250" t="s" s="2">
         <v>413</v>
@@ -32416,13 +32423,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D251" t="s" s="2">
         <v>79</v>
@@ -32444,7 +32451,7 @@
         <v>79</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L251" t="s" s="2">
         <v>414</v>
@@ -32535,13 +32542,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>465</v>
+        <v>729</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>79</v>
@@ -32551,7 +32558,7 @@
         <v>80</v>
       </c>
       <c r="G252" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H252" t="s" s="2">
         <v>79</v>
@@ -32563,7 +32570,7 @@
         <v>79</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>466</v>
+        <v>730</v>
       </c>
       <c r="L252" t="s" s="2">
         <v>414</v>
@@ -32654,12 +32661,14 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C253" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C253" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D253" t="s" s="2">
         <v>79</v>
       </c>
@@ -32668,7 +32677,7 @@
         <v>80</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H253" t="s" s="2">
         <v>79</v>
@@ -32680,20 +32689,18 @@
         <v>79</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
         <v>79</v>
       </c>
@@ -32717,13 +32724,13 @@
         <v>79</v>
       </c>
       <c r="X253" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y253" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z253" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA253" t="s" s="2">
         <v>79</v>
@@ -32741,13 +32748,13 @@
         <v>79</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI253" t="s" s="2">
         <v>417</v>
@@ -32759,10 +32766,10 @@
         <v>79</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>79</v>
@@ -32773,10 +32780,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32787,7 +32794,7 @@
         <v>80</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H254" t="s" s="2">
         <v>79</v>
@@ -32799,18 +32806,20 @@
         <v>79</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O254" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O254" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P254" t="s" s="2">
         <v>79</v>
       </c>
@@ -32834,13 +32843,13 @@
         <v>79</v>
       </c>
       <c r="X254" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y254" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z254" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>79</v>
@@ -32858,16 +32867,16 @@
         <v>79</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>103</v>
@@ -32876,10 +32885,10 @@
         <v>79</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>79</v>
@@ -32890,14 +32899,12 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
         <v>79</v>
       </c>
@@ -32906,7 +32913,7 @@
         <v>80</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>79</v>
@@ -32918,15 +32925,17 @@
         <v>79</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>734</v>
+        <v>429</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="N255" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>79</v>
@@ -32975,7 +32984,7 @@
         <v>79</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
@@ -32984,10 +32993,10 @@
         <v>81</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>79</v>
@@ -32996,7 +33005,7 @@
         <v>365</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN255" t="s" s="2">
         <v>79</v>
@@ -33007,12 +33016,14 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C256" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>735</v>
+      </c>
       <c r="D256" t="s" s="2">
         <v>79</v>
       </c>
@@ -33033,13 +33044,13 @@
         <v>79</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>262</v>
+        <v>736</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>263</v>
+        <v>737</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
@@ -33090,28 +33101,28 @@
         <v>79</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI256" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN256" t="s" s="2">
         <v>79</v>
@@ -33122,21 +33133,21 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H257" t="s" s="2">
         <v>79</v>
@@ -33148,17 +33159,15 @@
         <v>79</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N257" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N257" s="2"/>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
         <v>79</v>
@@ -33207,19 +33216,19 @@
         <v>79</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>79</v>
@@ -33239,14 +33248,14 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
@@ -33259,26 +33268,24 @@
         <v>79</v>
       </c>
       <c r="I258" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J258" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K258" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N258" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O258" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>79</v>
       </c>
@@ -33326,7 +33333,7 @@
         <v>79</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -33344,7 +33351,7 @@
         <v>79</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>79</v>
@@ -33358,45 +33365,45 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G259" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I259" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J259" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>79</v>
@@ -33445,28 +33452,28 @@
         <v>79</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN259" t="s" s="2">
         <v>79</v>
@@ -33477,18 +33484,18 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G260" t="s" s="2">
         <v>91</v>
@@ -33503,19 +33510,19 @@
         <v>79</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N260" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O260" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P260" t="s" s="2">
         <v>79</v>
@@ -33525,7 +33532,7 @@
         <v>79</v>
       </c>
       <c r="S260" t="s" s="2">
-        <v>741</v>
+        <v>79</v>
       </c>
       <c r="T260" t="s" s="2">
         <v>79</v>
@@ -33540,13 +33547,13 @@
         <v>79</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y260" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z260" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>79</v>
@@ -33564,7 +33571,7 @@
         <v>79</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>80</v>
@@ -33582,10 +33589,10 @@
         <v>79</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>79</v>
@@ -33599,7 +33606,7 @@
         <v>742</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33607,10 +33614,10 @@
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G261" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H261" t="s" s="2">
         <v>79</v>
@@ -33622,17 +33629,19 @@
         <v>79</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N261" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O261" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P261" t="s" s="2">
         <v>79</v>
@@ -33642,7 +33651,7 @@
         <v>79</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>79</v>
+        <v>743</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>79</v>
@@ -33657,13 +33666,13 @@
         <v>79</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>79</v>
@@ -33681,13 +33690,13 @@
         <v>79</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH261" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI261" t="s" s="2">
         <v>79</v>
@@ -33699,24 +33708,24 @@
         <v>79</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO261" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33727,7 +33736,7 @@
         <v>80</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>79</v>
@@ -33739,18 +33748,18 @@
         <v>79</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N262" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O262" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N262" s="2"/>
+      <c r="O262" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P262" t="s" s="2">
         <v>79</v>
       </c>
@@ -33798,13 +33807,13 @@
         <v>79</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI262" t="s" s="2">
         <v>79</v>
@@ -33816,24 +33825,24 @@
         <v>79</v>
       </c>
       <c r="AL262" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN262" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO262" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33856,16 +33865,16 @@
         <v>79</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -33915,7 +33924,7 @@
         <v>79</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
@@ -33924,7 +33933,7 @@
         <v>91</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>103</v>
@@ -33933,10 +33942,10 @@
         <v>79</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>79</v>
@@ -33947,10 +33956,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -33973,20 +33982,18 @@
         <v>79</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O264" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>79</v>
       </c>
@@ -34010,13 +34017,13 @@
         <v>79</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y264" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z264" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>79</v>
@@ -34034,7 +34041,7 @@
         <v>79</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -34043,7 +34050,7 @@
         <v>91</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>103</v>
@@ -34052,24 +34059,24 @@
         <v>79</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN264" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO264" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34092,19 +34099,19 @@
         <v>79</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>79</v>
@@ -34129,13 +34136,13 @@
         <v>79</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>79</v>
@@ -34153,7 +34160,7 @@
         <v>79</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>80</v>
@@ -34171,7 +34178,7 @@
         <v>79</v>
       </c>
       <c r="AL265" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM265" t="s" s="2">
         <v>168</v>
@@ -34180,15 +34187,15 @@
         <v>79</v>
       </c>
       <c r="AO265" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34199,7 +34206,7 @@
         <v>80</v>
       </c>
       <c r="G266" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H266" t="s" s="2">
         <v>79</v>
@@ -34211,18 +34218,20 @@
         <v>79</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>748</v>
+        <v>172</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O266" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O266" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P266" t="s" s="2">
         <v>79</v>
       </c>
@@ -34246,38 +34255,40 @@
         <v>79</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y266" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z266" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB266" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC266" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD266" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE266" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI266" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ266" t="s" s="2">
         <v>103</v>
@@ -34286,10 +34297,10 @@
         <v>79</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>79</v>
@@ -34305,9 +34316,7 @@
       <c r="B267" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C267" t="s" s="2">
-        <v>750</v>
-      </c>
+      <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
         <v>79</v>
       </c>
@@ -34328,7 +34337,7 @@
         <v>79</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="L267" t="s" s="2">
         <v>414</v>
@@ -34375,16 +34384,14 @@
         <v>79</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC267" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC267" s="2"/>
       <c r="AD267" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF267" t="s" s="2">
         <v>413</v>
@@ -34419,13 +34426,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D268" t="s" s="2">
         <v>79</v>
@@ -34447,7 +34454,7 @@
         <v>79</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="L268" t="s" s="2">
         <v>414</v>
@@ -34538,13 +34545,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>465</v>
+        <v>755</v>
       </c>
       <c r="D269" t="s" s="2">
         <v>79</v>
@@ -34566,7 +34573,7 @@
         <v>79</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>466</v>
+        <v>756</v>
       </c>
       <c r="L269" t="s" s="2">
         <v>414</v>
@@ -34657,12 +34664,14 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C270" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C270" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D270" t="s" s="2">
         <v>79</v>
       </c>
@@ -34671,7 +34680,7 @@
         <v>80</v>
       </c>
       <c r="G270" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H270" t="s" s="2">
         <v>79</v>
@@ -34683,20 +34692,18 @@
         <v>79</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O270" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O270" s="2"/>
       <c r="P270" t="s" s="2">
         <v>79</v>
       </c>
@@ -34720,13 +34727,13 @@
         <v>79</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>79</v>
@@ -34744,13 +34751,13 @@
         <v>79</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH270" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI270" t="s" s="2">
         <v>417</v>
@@ -34762,10 +34769,10 @@
         <v>79</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM270" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN270" t="s" s="2">
         <v>79</v>
@@ -34776,10 +34783,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34790,7 +34797,7 @@
         <v>80</v>
       </c>
       <c r="G271" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H271" t="s" s="2">
         <v>79</v>
@@ -34802,18 +34809,20 @@
         <v>79</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O271" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O271" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P271" t="s" s="2">
         <v>79</v>
       </c>
@@ -34837,13 +34846,13 @@
         <v>79</v>
       </c>
       <c r="X271" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y271" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z271" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA271" t="s" s="2">
         <v>79</v>
@@ -34861,16 +34870,16 @@
         <v>79</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH271" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>103</v>
@@ -34879,10 +34888,10 @@
         <v>79</v>
       </c>
       <c r="AL271" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>79</v>
@@ -34893,14 +34902,12 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>759</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
         <v>79</v>
       </c>
@@ -34909,7 +34916,7 @@
         <v>80</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H272" t="s" s="2">
         <v>79</v>
@@ -34921,15 +34928,17 @@
         <v>79</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>760</v>
+        <v>429</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="N272" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
         <v>79</v>
@@ -34978,7 +34987,7 @@
         <v>79</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>80</v>
@@ -34987,10 +34996,10 @@
         <v>81</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK272" t="s" s="2">
         <v>79</v>
@@ -34999,7 +35008,7 @@
         <v>365</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN272" t="s" s="2">
         <v>79</v>
@@ -35010,12 +35019,14 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C273" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C273" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="D273" t="s" s="2">
         <v>79</v>
       </c>
@@ -35036,13 +35047,13 @@
         <v>79</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>262</v>
+        <v>762</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>263</v>
+        <v>763</v>
       </c>
       <c r="N273" s="2"/>
       <c r="O273" s="2"/>
@@ -35093,28 +35104,28 @@
         <v>79</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI273" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL273" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM273" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN273" t="s" s="2">
         <v>79</v>
@@ -35125,21 +35136,21 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>79</v>
@@ -35151,17 +35162,15 @@
         <v>79</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N274" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N274" s="2"/>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
         <v>79</v>
@@ -35210,19 +35219,19 @@
         <v>79</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI274" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>79</v>
@@ -35242,14 +35251,14 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
@@ -35262,26 +35271,24 @@
         <v>79</v>
       </c>
       <c r="I275" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K275" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N275" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O275" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
         <v>79</v>
       </c>
@@ -35329,7 +35336,7 @@
         <v>79</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>80</v>
@@ -35347,7 +35354,7 @@
         <v>79</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM275" t="s" s="2">
         <v>79</v>
@@ -35361,45 +35368,45 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G276" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I276" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J276" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O276" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>79</v>
@@ -35448,28 +35455,28 @@
         <v>79</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ276" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL276" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN276" t="s" s="2">
         <v>79</v>
@@ -35480,18 +35487,18 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G277" t="s" s="2">
         <v>91</v>
@@ -35506,19 +35513,19 @@
         <v>79</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O277" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P277" t="s" s="2">
         <v>79</v>
@@ -35528,7 +35535,7 @@
         <v>79</v>
       </c>
       <c r="S277" t="s" s="2">
-        <v>767</v>
+        <v>79</v>
       </c>
       <c r="T277" t="s" s="2">
         <v>79</v>
@@ -35543,13 +35550,13 @@
         <v>79</v>
       </c>
       <c r="X277" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y277" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z277" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>79</v>
@@ -35567,7 +35574,7 @@
         <v>79</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>80</v>
@@ -35585,10 +35592,10 @@
         <v>79</v>
       </c>
       <c r="AL277" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN277" t="s" s="2">
         <v>79</v>
@@ -35602,7 +35609,7 @@
         <v>768</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35610,10 +35617,10 @@
       </c>
       <c r="E278" s="2"/>
       <c r="F278" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G278" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H278" t="s" s="2">
         <v>79</v>
@@ -35625,17 +35632,19 @@
         <v>79</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N278" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N278" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O278" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P278" t="s" s="2">
         <v>79</v>
@@ -35645,7 +35654,7 @@
         <v>79</v>
       </c>
       <c r="S278" t="s" s="2">
-        <v>79</v>
+        <v>769</v>
       </c>
       <c r="T278" t="s" s="2">
         <v>79</v>
@@ -35660,13 +35669,13 @@
         <v>79</v>
       </c>
       <c r="X278" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y278" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z278" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA278" t="s" s="2">
         <v>79</v>
@@ -35684,13 +35693,13 @@
         <v>79</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH278" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI278" t="s" s="2">
         <v>79</v>
@@ -35702,24 +35711,24 @@
         <v>79</v>
       </c>
       <c r="AL278" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO278" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35730,7 +35739,7 @@
         <v>80</v>
       </c>
       <c r="G279" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>79</v>
@@ -35742,18 +35751,18 @@
         <v>79</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O279" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N279" s="2"/>
+      <c r="O279" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P279" t="s" s="2">
         <v>79</v>
       </c>
@@ -35801,13 +35810,13 @@
         <v>79</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>79</v>
@@ -35819,24 +35828,24 @@
         <v>79</v>
       </c>
       <c r="AL279" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO279" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35859,16 +35868,16 @@
         <v>79</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" t="s" s="2">
@@ -35918,7 +35927,7 @@
         <v>79</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>80</v>
@@ -35927,7 +35936,7 @@
         <v>91</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>103</v>
@@ -35936,10 +35945,10 @@
         <v>79</v>
       </c>
       <c r="AL280" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM280" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN280" t="s" s="2">
         <v>79</v>
@@ -35950,10 +35959,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -35976,20 +35985,18 @@
         <v>79</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
         <v>79</v>
       </c>
@@ -36013,13 +36020,13 @@
         <v>79</v>
       </c>
       <c r="X281" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y281" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z281" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>79</v>
@@ -36037,7 +36044,7 @@
         <v>79</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -36046,7 +36053,7 @@
         <v>91</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>103</v>
@@ -36055,24 +36062,24 @@
         <v>79</v>
       </c>
       <c r="AL281" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO281" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -36095,19 +36102,19 @@
         <v>79</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O282" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P282" t="s" s="2">
         <v>79</v>
@@ -36132,13 +36139,13 @@
         <v>79</v>
       </c>
       <c r="X282" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y282" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>79</v>
@@ -36156,7 +36163,7 @@
         <v>79</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>80</v>
@@ -36174,7 +36181,7 @@
         <v>79</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM282" t="s" s="2">
         <v>168</v>
@@ -36183,15 +36190,15 @@
         <v>79</v>
       </c>
       <c r="AO282" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36202,7 +36209,7 @@
         <v>80</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>79</v>
@@ -36214,18 +36221,20 @@
         <v>79</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>774</v>
+        <v>172</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O283" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O283" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P283" t="s" s="2">
         <v>79</v>
       </c>
@@ -36249,38 +36258,40 @@
         <v>79</v>
       </c>
       <c r="X283" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y283" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z283" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA283" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB283" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC283" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC283" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD283" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE283" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>103</v>
@@ -36289,10 +36300,10 @@
         <v>79</v>
       </c>
       <c r="AL283" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM283" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN283" t="s" s="2">
         <v>79</v>
@@ -36308,9 +36319,7 @@
       <c r="B284" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C284" t="s" s="2">
-        <v>776</v>
-      </c>
+      <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
         <v>79</v>
       </c>
@@ -36331,7 +36340,7 @@
         <v>79</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L284" t="s" s="2">
         <v>414</v>
@@ -36378,16 +36387,14 @@
         <v>79</v>
       </c>
       <c r="AB284" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC284" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC284" s="2"/>
       <c r="AD284" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE284" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF284" t="s" s="2">
         <v>413</v>
@@ -36422,13 +36429,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>465</v>
+        <v>778</v>
       </c>
       <c r="D285" t="s" s="2">
         <v>79</v>
@@ -36450,7 +36457,7 @@
         <v>79</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>466</v>
+        <v>779</v>
       </c>
       <c r="L285" t="s" s="2">
         <v>414</v>
@@ -36541,12 +36548,14 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C286" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C286" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D286" t="s" s="2">
         <v>79</v>
       </c>
@@ -36555,7 +36564,7 @@
         <v>80</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H286" t="s" s="2">
         <v>79</v>
@@ -36567,20 +36576,18 @@
         <v>79</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O286" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O286" s="2"/>
       <c r="P286" t="s" s="2">
         <v>79</v>
       </c>
@@ -36604,13 +36611,13 @@
         <v>79</v>
       </c>
       <c r="X286" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y286" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z286" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA286" t="s" s="2">
         <v>79</v>
@@ -36628,13 +36635,13 @@
         <v>79</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH286" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI286" t="s" s="2">
         <v>417</v>
@@ -36646,10 +36653,10 @@
         <v>79</v>
       </c>
       <c r="AL286" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>79</v>
@@ -36660,10 +36667,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36674,7 +36681,7 @@
         <v>80</v>
       </c>
       <c r="G287" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H287" t="s" s="2">
         <v>79</v>
@@ -36686,18 +36693,20 @@
         <v>79</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O287" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O287" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P287" t="s" s="2">
         <v>79</v>
       </c>
@@ -36721,13 +36730,13 @@
         <v>79</v>
       </c>
       <c r="X287" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y287" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z287" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>79</v>
@@ -36745,16 +36754,16 @@
         <v>79</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH287" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI287" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ287" t="s" s="2">
         <v>103</v>
@@ -36763,10 +36772,10 @@
         <v>79</v>
       </c>
       <c r="AL287" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN287" t="s" s="2">
         <v>79</v>
@@ -36777,14 +36786,12 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>782</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>79</v>
       </c>
@@ -36793,7 +36800,7 @@
         <v>80</v>
       </c>
       <c r="G288" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H288" t="s" s="2">
         <v>79</v>
@@ -36805,15 +36812,17 @@
         <v>79</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>783</v>
+        <v>429</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N288" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N288" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
         <v>79</v>
@@ -36862,7 +36871,7 @@
         <v>79</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>80</v>
@@ -36871,10 +36880,10 @@
         <v>81</v>
       </c>
       <c r="AI288" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ288" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK288" t="s" s="2">
         <v>79</v>
@@ -36883,7 +36892,7 @@
         <v>365</v>
       </c>
       <c r="AM288" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN288" t="s" s="2">
         <v>79</v>
@@ -36894,12 +36903,14 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C289" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C289" t="s" s="2">
+        <v>784</v>
+      </c>
       <c r="D289" t="s" s="2">
         <v>79</v>
       </c>
@@ -36920,13 +36931,13 @@
         <v>79</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>262</v>
+        <v>785</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>263</v>
+        <v>786</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -36977,28 +36988,28 @@
         <v>79</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH289" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI289" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL289" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>79</v>
@@ -37009,21 +37020,21 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G290" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H290" t="s" s="2">
         <v>79</v>
@@ -37035,17 +37046,15 @@
         <v>79</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N290" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N290" s="2"/>
       <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>79</v>
@@ -37094,19 +37103,19 @@
         <v>79</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH290" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI290" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>79</v>
@@ -37126,14 +37135,14 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" t="s" s="2">
@@ -37146,26 +37155,24 @@
         <v>79</v>
       </c>
       <c r="I291" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J291" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K291" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N291" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O291" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
         <v>79</v>
       </c>
@@ -37213,7 +37220,7 @@
         <v>79</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>80</v>
@@ -37231,7 +37238,7 @@
         <v>79</v>
       </c>
       <c r="AL291" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM291" t="s" s="2">
         <v>79</v>
@@ -37245,45 +37252,45 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I292" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J292" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O292" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P292" t="s" s="2">
         <v>79</v>
@@ -37332,28 +37339,28 @@
         <v>79</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL292" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM292" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN292" t="s" s="2">
         <v>79</v>
@@ -37364,18 +37371,18 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G293" t="s" s="2">
         <v>91</v>
@@ -37390,19 +37397,19 @@
         <v>79</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O293" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P293" t="s" s="2">
         <v>79</v>
@@ -37412,7 +37419,7 @@
         <v>79</v>
       </c>
       <c r="S293" t="s" s="2">
-        <v>790</v>
+        <v>79</v>
       </c>
       <c r="T293" t="s" s="2">
         <v>79</v>
@@ -37427,13 +37434,13 @@
         <v>79</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y293" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z293" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>79</v>
@@ -37451,7 +37458,7 @@
         <v>79</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>80</v>
@@ -37469,10 +37476,10 @@
         <v>79</v>
       </c>
       <c r="AL293" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM293" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN293" t="s" s="2">
         <v>79</v>
@@ -37486,7 +37493,7 @@
         <v>791</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37494,10 +37501,10 @@
       </c>
       <c r="E294" s="2"/>
       <c r="F294" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G294" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H294" t="s" s="2">
         <v>79</v>
@@ -37509,17 +37516,19 @@
         <v>79</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N294" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N294" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O294" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>79</v>
@@ -37529,7 +37538,7 @@
         <v>79</v>
       </c>
       <c r="S294" t="s" s="2">
-        <v>79</v>
+        <v>792</v>
       </c>
       <c r="T294" t="s" s="2">
         <v>79</v>
@@ -37544,13 +37553,13 @@
         <v>79</v>
       </c>
       <c r="X294" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y294" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z294" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA294" t="s" s="2">
         <v>79</v>
@@ -37568,13 +37577,13 @@
         <v>79</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH294" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI294" t="s" s="2">
         <v>79</v>
@@ -37586,24 +37595,24 @@
         <v>79</v>
       </c>
       <c r="AL294" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN294" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO294" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37614,7 +37623,7 @@
         <v>80</v>
       </c>
       <c r="G295" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H295" t="s" s="2">
         <v>79</v>
@@ -37626,18 +37635,18 @@
         <v>79</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N295" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O295" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N295" s="2"/>
+      <c r="O295" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P295" t="s" s="2">
         <v>79</v>
       </c>
@@ -37685,13 +37694,13 @@
         <v>79</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH295" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI295" t="s" s="2">
         <v>79</v>
@@ -37703,24 +37712,24 @@
         <v>79</v>
       </c>
       <c r="AL295" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM295" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN295" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO295" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37743,16 +37752,16 @@
         <v>79</v>
       </c>
       <c r="K296" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
@@ -37802,7 +37811,7 @@
         <v>79</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>80</v>
@@ -37811,7 +37820,7 @@
         <v>91</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>103</v>
@@ -37820,10 +37829,10 @@
         <v>79</v>
       </c>
       <c r="AL296" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>79</v>
@@ -37834,10 +37843,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37860,20 +37869,18 @@
         <v>79</v>
       </c>
       <c r="K297" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O297" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O297" s="2"/>
       <c r="P297" t="s" s="2">
         <v>79</v>
       </c>
@@ -37897,13 +37904,13 @@
         <v>79</v>
       </c>
       <c r="X297" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y297" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z297" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA297" t="s" s="2">
         <v>79</v>
@@ -37921,7 +37928,7 @@
         <v>79</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG297" t="s" s="2">
         <v>80</v>
@@ -37930,7 +37937,7 @@
         <v>91</v>
       </c>
       <c r="AI297" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ297" t="s" s="2">
         <v>103</v>
@@ -37939,24 +37946,24 @@
         <v>79</v>
       </c>
       <c r="AL297" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM297" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN297" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO297" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -37979,19 +37986,19 @@
         <v>79</v>
       </c>
       <c r="K298" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O298" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P298" t="s" s="2">
         <v>79</v>
@@ -38016,13 +38023,13 @@
         <v>79</v>
       </c>
       <c r="X298" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y298" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z298" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA298" t="s" s="2">
         <v>79</v>
@@ -38040,7 +38047,7 @@
         <v>79</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>80</v>
@@ -38058,7 +38065,7 @@
         <v>79</v>
       </c>
       <c r="AL298" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM298" t="s" s="2">
         <v>168</v>
@@ -38067,15 +38074,15 @@
         <v>79</v>
       </c>
       <c r="AO298" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38086,7 +38093,7 @@
         <v>80</v>
       </c>
       <c r="G299" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H299" t="s" s="2">
         <v>79</v>
@@ -38098,18 +38105,20 @@
         <v>79</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>797</v>
+        <v>172</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O299" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O299" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P299" t="s" s="2">
         <v>79</v>
       </c>
@@ -38133,38 +38142,40 @@
         <v>79</v>
       </c>
       <c r="X299" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y299" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z299" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA299" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB299" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC299" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC299" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD299" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE299" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH299" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI299" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ299" t="s" s="2">
         <v>103</v>
@@ -38173,10 +38184,10 @@
         <v>79</v>
       </c>
       <c r="AL299" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>79</v>
@@ -38192,9 +38203,7 @@
       <c r="B300" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C300" t="s" s="2">
-        <v>799</v>
-      </c>
+      <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
         <v>79</v>
       </c>
@@ -38215,7 +38224,7 @@
         <v>79</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L300" t="s" s="2">
         <v>414</v>
@@ -38262,16 +38271,14 @@
         <v>79</v>
       </c>
       <c r="AB300" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC300" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC300" s="2"/>
       <c r="AD300" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE300" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF300" t="s" s="2">
         <v>413</v>
@@ -38306,13 +38313,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>465</v>
+        <v>801</v>
       </c>
       <c r="D301" t="s" s="2">
         <v>79</v>
@@ -38334,7 +38341,7 @@
         <v>79</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>466</v>
+        <v>802</v>
       </c>
       <c r="L301" t="s" s="2">
         <v>414</v>
@@ -38425,12 +38432,14 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C302" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C302" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D302" t="s" s="2">
         <v>79</v>
       </c>
@@ -38439,7 +38448,7 @@
         <v>80</v>
       </c>
       <c r="G302" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H302" t="s" s="2">
         <v>79</v>
@@ -38451,20 +38460,18 @@
         <v>79</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>172</v>
+        <v>465</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O302" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O302" s="2"/>
       <c r="P302" t="s" s="2">
         <v>79</v>
       </c>
@@ -38488,13 +38495,13 @@
         <v>79</v>
       </c>
       <c r="X302" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y302" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z302" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA302" t="s" s="2">
         <v>79</v>
@@ -38512,13 +38519,13 @@
         <v>79</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH302" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI302" t="s" s="2">
         <v>417</v>
@@ -38530,10 +38537,10 @@
         <v>79</v>
       </c>
       <c r="AL302" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM302" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN302" t="s" s="2">
         <v>79</v>
@@ -38544,10 +38551,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -38558,7 +38565,7 @@
         <v>80</v>
       </c>
       <c r="G303" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H303" t="s" s="2">
         <v>79</v>
@@ -38570,18 +38577,20 @@
         <v>79</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O303" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O303" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P303" t="s" s="2">
         <v>79</v>
       </c>
@@ -38605,13 +38614,13 @@
         <v>79</v>
       </c>
       <c r="X303" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y303" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z303" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA303" t="s" s="2">
         <v>79</v>
@@ -38629,16 +38638,16 @@
         <v>79</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH303" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI303" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ303" t="s" s="2">
         <v>103</v>
@@ -38647,10 +38656,10 @@
         <v>79</v>
       </c>
       <c r="AL303" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM303" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN303" t="s" s="2">
         <v>79</v>
@@ -38661,14 +38670,12 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C304" t="s" s="2">
-        <v>805</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
         <v>79</v>
       </c>
@@ -38677,7 +38684,7 @@
         <v>80</v>
       </c>
       <c r="G304" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H304" t="s" s="2">
         <v>79</v>
@@ -38689,15 +38696,17 @@
         <v>79</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>806</v>
+        <v>429</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="N304" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N304" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O304" s="2"/>
       <c r="P304" t="s" s="2">
         <v>79</v>
@@ -38746,7 +38755,7 @@
         <v>79</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>80</v>
@@ -38755,10 +38764,10 @@
         <v>81</v>
       </c>
       <c r="AI304" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ304" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK304" t="s" s="2">
         <v>79</v>
@@ -38767,7 +38776,7 @@
         <v>365</v>
       </c>
       <c r="AM304" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN304" t="s" s="2">
         <v>79</v>
@@ -38778,12 +38787,14 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C305" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C305" t="s" s="2">
+        <v>807</v>
+      </c>
       <c r="D305" t="s" s="2">
         <v>79</v>
       </c>
@@ -38804,13 +38815,13 @@
         <v>79</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>262</v>
+        <v>808</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>263</v>
+        <v>809</v>
       </c>
       <c r="N305" s="2"/>
       <c r="O305" s="2"/>
@@ -38861,28 +38872,28 @@
         <v>79</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH305" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI305" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ305" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK305" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL305" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM305" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN305" t="s" s="2">
         <v>79</v>
@@ -38893,21 +38904,21 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E306" s="2"/>
       <c r="F306" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G306" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H306" t="s" s="2">
         <v>79</v>
@@ -38919,17 +38930,15 @@
         <v>79</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N306" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N306" s="2"/>
       <c r="O306" s="2"/>
       <c r="P306" t="s" s="2">
         <v>79</v>
@@ -38978,19 +38987,19 @@
         <v>79</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH306" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI306" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ306" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK306" t="s" s="2">
         <v>79</v>
@@ -39010,14 +39019,14 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E307" s="2"/>
       <c r="F307" t="s" s="2">
@@ -39030,26 +39039,24 @@
         <v>79</v>
       </c>
       <c r="I307" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J307" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K307" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N307" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O307" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O307" s="2"/>
       <c r="P307" t="s" s="2">
         <v>79</v>
       </c>
@@ -39097,7 +39104,7 @@
         <v>79</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>80</v>
@@ -39115,7 +39122,7 @@
         <v>79</v>
       </c>
       <c r="AL307" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM307" t="s" s="2">
         <v>79</v>
@@ -39129,45 +39136,45 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E308" s="2"/>
       <c r="F308" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G308" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I308" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J308" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K308" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O308" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P308" t="s" s="2">
         <v>79</v>
@@ -39216,28 +39223,28 @@
         <v>79</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH308" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ308" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL308" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM308" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN308" t="s" s="2">
         <v>79</v>
@@ -39248,18 +39255,18 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E309" s="2"/>
       <c r="F309" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G309" t="s" s="2">
         <v>91</v>
@@ -39274,19 +39281,19 @@
         <v>79</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O309" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P309" t="s" s="2">
         <v>79</v>
@@ -39296,7 +39303,7 @@
         <v>79</v>
       </c>
       <c r="S309" t="s" s="2">
-        <v>813</v>
+        <v>79</v>
       </c>
       <c r="T309" t="s" s="2">
         <v>79</v>
@@ -39311,13 +39318,13 @@
         <v>79</v>
       </c>
       <c r="X309" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y309" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z309" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA309" t="s" s="2">
         <v>79</v>
@@ -39335,7 +39342,7 @@
         <v>79</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>80</v>
@@ -39353,10 +39360,10 @@
         <v>79</v>
       </c>
       <c r="AL309" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM309" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN309" t="s" s="2">
         <v>79</v>
@@ -39370,7 +39377,7 @@
         <v>814</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -39378,10 +39385,10 @@
       </c>
       <c r="E310" s="2"/>
       <c r="F310" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G310" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H310" t="s" s="2">
         <v>79</v>
@@ -39393,17 +39400,19 @@
         <v>79</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N310" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N310" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O310" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P310" t="s" s="2">
         <v>79</v>
@@ -39413,7 +39422,7 @@
         <v>79</v>
       </c>
       <c r="S310" t="s" s="2">
-        <v>79</v>
+        <v>815</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>79</v>
@@ -39428,13 +39437,13 @@
         <v>79</v>
       </c>
       <c r="X310" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y310" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z310" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA310" t="s" s="2">
         <v>79</v>
@@ -39452,13 +39461,13 @@
         <v>79</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH310" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI310" t="s" s="2">
         <v>79</v>
@@ -39470,24 +39479,24 @@
         <v>79</v>
       </c>
       <c r="AL310" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM310" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN310" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO310" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -39498,7 +39507,7 @@
         <v>80</v>
       </c>
       <c r="G311" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H311" t="s" s="2">
         <v>79</v>
@@ -39510,18 +39519,18 @@
         <v>79</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N311" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O311" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N311" s="2"/>
+      <c r="O311" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P311" t="s" s="2">
         <v>79</v>
       </c>
@@ -39569,13 +39578,13 @@
         <v>79</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH311" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI311" t="s" s="2">
         <v>79</v>
@@ -39587,24 +39596,24 @@
         <v>79</v>
       </c>
       <c r="AL311" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM311" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN311" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO311" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -39627,16 +39636,16 @@
         <v>79</v>
       </c>
       <c r="K312" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
@@ -39686,7 +39695,7 @@
         <v>79</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>80</v>
@@ -39695,7 +39704,7 @@
         <v>91</v>
       </c>
       <c r="AI312" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ312" t="s" s="2">
         <v>103</v>
@@ -39704,10 +39713,10 @@
         <v>79</v>
       </c>
       <c r="AL312" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM312" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN312" t="s" s="2">
         <v>79</v>
@@ -39718,10 +39727,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -39744,20 +39753,18 @@
         <v>79</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O313" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O313" s="2"/>
       <c r="P313" t="s" s="2">
         <v>79</v>
       </c>
@@ -39781,13 +39788,13 @@
         <v>79</v>
       </c>
       <c r="X313" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y313" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z313" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA313" t="s" s="2">
         <v>79</v>
@@ -39805,7 +39812,7 @@
         <v>79</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>80</v>
@@ -39814,7 +39821,7 @@
         <v>91</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ313" t="s" s="2">
         <v>103</v>
@@ -39823,24 +39830,24 @@
         <v>79</v>
       </c>
       <c r="AL313" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM313" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN313" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO313" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -39863,19 +39870,19 @@
         <v>79</v>
       </c>
       <c r="K314" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O314" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P314" t="s" s="2">
         <v>79</v>
@@ -39900,13 +39907,13 @@
         <v>79</v>
       </c>
       <c r="X314" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y314" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z314" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA314" t="s" s="2">
         <v>79</v>
@@ -39924,7 +39931,7 @@
         <v>79</v>
       </c>
       <c r="AF314" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG314" t="s" s="2">
         <v>80</v>
@@ -39942,7 +39949,7 @@
         <v>79</v>
       </c>
       <c r="AL314" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM314" t="s" s="2">
         <v>168</v>
@@ -39951,15 +39958,15 @@
         <v>79</v>
       </c>
       <c r="AO314" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -39970,7 +39977,7 @@
         <v>80</v>
       </c>
       <c r="G315" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H315" t="s" s="2">
         <v>79</v>
@@ -39982,18 +39989,20 @@
         <v>79</v>
       </c>
       <c r="K315" t="s" s="2">
-        <v>354</v>
+        <v>172</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O315" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O315" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P315" t="s" s="2">
         <v>79</v>
       </c>
@@ -40017,13 +40026,13 @@
         <v>79</v>
       </c>
       <c r="X315" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y315" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z315" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA315" t="s" s="2">
         <v>79</v>
@@ -40041,16 +40050,16 @@
         <v>79</v>
       </c>
       <c r="AF315" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG315" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH315" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI315" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ315" t="s" s="2">
         <v>103</v>
@@ -40059,10 +40068,10 @@
         <v>79</v>
       </c>
       <c r="AL315" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM315" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN315" t="s" s="2">
         <v>79</v>
@@ -40073,10 +40082,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -40087,7 +40096,7 @@
         <v>80</v>
       </c>
       <c r="G316" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H316" t="s" s="2">
         <v>79</v>
@@ -40099,20 +40108,18 @@
         <v>79</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>172</v>
+        <v>354</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O316" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O316" s="2"/>
       <c r="P316" t="s" s="2">
         <v>79</v>
       </c>
@@ -40136,13 +40143,13 @@
         <v>79</v>
       </c>
       <c r="X316" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y316" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z316" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA316" t="s" s="2">
         <v>79</v>
@@ -40160,13 +40167,13 @@
         <v>79</v>
       </c>
       <c r="AF316" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG316" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH316" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI316" t="s" s="2">
         <v>417</v>
@@ -40178,10 +40185,10 @@
         <v>79</v>
       </c>
       <c r="AL316" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM316" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN316" t="s" s="2">
         <v>79</v>
@@ -40192,10 +40199,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -40206,7 +40213,7 @@
         <v>80</v>
       </c>
       <c r="G317" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H317" t="s" s="2">
         <v>79</v>
@@ -40218,18 +40225,20 @@
         <v>79</v>
       </c>
       <c r="K317" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O317" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O317" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P317" t="s" s="2">
         <v>79</v>
       </c>
@@ -40253,13 +40262,13 @@
         <v>79</v>
       </c>
       <c r="X317" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y317" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z317" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA317" t="s" s="2">
         <v>79</v>
@@ -40277,16 +40286,16 @@
         <v>79</v>
       </c>
       <c r="AF317" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG317" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH317" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI317" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ317" t="s" s="2">
         <v>103</v>
@@ -40295,15 +40304,132 @@
         <v>79</v>
       </c>
       <c r="AL317" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM317" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AN317" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO317" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B318" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C318" s="2"/>
+      <c r="D318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E318" s="2"/>
+      <c r="F318" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G318" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K318" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L318" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M318" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N318" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O318" s="2"/>
+      <c r="P318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q318" s="2"/>
+      <c r="R318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF318" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG318" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH318" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI318" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AJ318" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL318" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM317" t="s" s="2">
+      <c r="AM318" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN317" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO317" t="s" s="2">
+      <c r="AN318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO318" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:21:15+00:00</t>
+    <t>2026-02-04T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:46:20+00:00</t>
+    <t>2026-02-05T06:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T08:33:30+00:00</t>
+    <t>2026-02-05T09:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-update-general-narrative/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T09:19:21+00:00</t>
+    <t>2026-02-05T09:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
